--- a/output/yearly_total_coral_cover_iteration_24_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_24_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.256810276303763</v>
+        <v>1.275060966125711</v>
       </c>
       <c r="C3" t="n">
-        <v>4.612198572983352</v>
+        <v>4.589912900096949</v>
       </c>
       <c r="D3" t="n">
-        <v>6.12138847071583</v>
+        <v>6.090532140371354</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99039732000294</v>
+        <v>11.95550600659401</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.378441825634376</v>
+        <v>1.428978371471767</v>
       </c>
       <c r="C4" t="n">
-        <v>5.084723666395841</v>
+        <v>4.996005041195627</v>
       </c>
       <c r="D4" t="n">
-        <v>6.358569014168038</v>
+        <v>6.340917895328012</v>
       </c>
       <c r="E4" t="n">
-        <v>12.82173450619826</v>
+        <v>12.7659013079954</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.541556639207371</v>
+        <v>1.629077335286161</v>
       </c>
       <c r="C5" t="n">
-        <v>5.652779791234578</v>
+        <v>5.477881023959051</v>
       </c>
       <c r="D5" t="n">
-        <v>6.690171752634</v>
+        <v>6.652358520160996</v>
       </c>
       <c r="E5" t="n">
-        <v>13.88450818307595</v>
+        <v>13.75931687940621</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.731463718269624</v>
+        <v>1.859792399268976</v>
       </c>
       <c r="C6" t="n">
-        <v>6.347249462448089</v>
+        <v>6.024707621575774</v>
       </c>
       <c r="D6" t="n">
-        <v>7.014072261453446</v>
+        <v>6.960599759071707</v>
       </c>
       <c r="E6" t="n">
-        <v>15.09278544217116</v>
+        <v>14.84509977991646</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.949688958154814</v>
+        <v>2.132440769056644</v>
       </c>
       <c r="C7" t="n">
-        <v>7.169243489855451</v>
+        <v>6.664251023173373</v>
       </c>
       <c r="D7" t="n">
-        <v>7.382948198027252</v>
+        <v>7.282582060514582</v>
       </c>
       <c r="E7" t="n">
-        <v>16.50188064603752</v>
+        <v>16.0792738527446</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.189862329567845</v>
+        <v>1.346305374554549</v>
       </c>
       <c r="C8" t="n">
-        <v>4.854307513675776</v>
+        <v>4.271084787716307</v>
       </c>
       <c r="D8" t="n">
-        <v>5.573308441793159</v>
+        <v>5.515830729315001</v>
       </c>
       <c r="E8" t="n">
-        <v>11.61747828503678</v>
+        <v>11.13322089158586</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.501558537512314</v>
+        <v>1.717807777775094</v>
       </c>
       <c r="C9" t="n">
-        <v>5.989355241780251</v>
+        <v>5.104862740965074</v>
       </c>
       <c r="D9" t="n">
-        <v>6.100828710691814</v>
+        <v>5.988413404084325</v>
       </c>
       <c r="E9" t="n">
-        <v>13.59174248998438</v>
+        <v>12.81108392282449</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.83802413325294</v>
+        <v>2.116087767268582</v>
       </c>
       <c r="C10" t="n">
-        <v>7.282073440652941</v>
+        <v>6.0796683860296</v>
       </c>
       <c r="D10" t="n">
-        <v>6.583753265673852</v>
+        <v>6.492002356976762</v>
       </c>
       <c r="E10" t="n">
-        <v>15.70385083957973</v>
+        <v>14.68775851027494</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.181498102567363</v>
+        <v>2.532340399485766</v>
       </c>
       <c r="C11" t="n">
-        <v>8.684205950302413</v>
+        <v>7.155222090467995</v>
       </c>
       <c r="D11" t="n">
-        <v>7.040144876420069</v>
+        <v>6.953260850350564</v>
       </c>
       <c r="E11" t="n">
-        <v>17.90584892928985</v>
+        <v>16.64082334030432</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.52747781619199</v>
+        <v>2.960599990926244</v>
       </c>
       <c r="C12" t="n">
-        <v>10.16322439616843</v>
+        <v>8.328122269085624</v>
       </c>
       <c r="D12" t="n">
-        <v>7.542995577488371</v>
+        <v>7.410924279531399</v>
       </c>
       <c r="E12" t="n">
-        <v>20.23369778984879</v>
+        <v>18.69964653954327</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.868689905811743</v>
+        <v>3.397490829692132</v>
       </c>
       <c r="C13" t="n">
-        <v>11.67429536471175</v>
+        <v>9.609075176853016</v>
       </c>
       <c r="D13" t="n">
-        <v>8.036142341081355</v>
+        <v>7.870372299650911</v>
       </c>
       <c r="E13" t="n">
-        <v>22.57912761160485</v>
+        <v>20.87693830619606</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.65509900215857</v>
+        <v>1.97621885874066</v>
       </c>
       <c r="C14" t="n">
-        <v>8.162368222832491</v>
+        <v>6.860924196174749</v>
       </c>
       <c r="D14" t="n">
-        <v>6.104301057988776</v>
+        <v>5.990447776727273</v>
       </c>
       <c r="E14" t="n">
-        <v>15.92176828297984</v>
+        <v>14.82759083164268</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.704372919434717</v>
+        <v>2.06214141781634</v>
       </c>
       <c r="C15" t="n">
-        <v>8.778120382936091</v>
+        <v>7.40197517346221</v>
       </c>
       <c r="D15" t="n">
-        <v>6.114687948699706</v>
+        <v>6.001443351014837</v>
       </c>
       <c r="E15" t="n">
-        <v>16.59718125107052</v>
+        <v>15.46555994229339</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.997336251859009</v>
+        <v>2.44237230367113</v>
       </c>
       <c r="C16" t="n">
-        <v>10.32299857033887</v>
+        <v>8.778189105275388</v>
       </c>
       <c r="D16" t="n">
-        <v>6.651753030307924</v>
+        <v>6.465957277279215</v>
       </c>
       <c r="E16" t="n">
-        <v>18.9720878525058</v>
+        <v>17.68651868622573</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.614916068623748</v>
+        <v>1.988107823439088</v>
       </c>
       <c r="C17" t="n">
-        <v>9.49693641703152</v>
+        <v>8.202030830084063</v>
       </c>
       <c r="D17" t="n">
-        <v>6.210830501376598</v>
+        <v>6.002199296747107</v>
       </c>
       <c r="E17" t="n">
-        <v>17.32268298703186</v>
+        <v>16.19233795027026</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.861207115188146</v>
+        <v>2.314951269136937</v>
       </c>
       <c r="C18" t="n">
-        <v>11.04056778484991</v>
+        <v>9.617004161260907</v>
       </c>
       <c r="D18" t="n">
-        <v>6.665222608810191</v>
+        <v>6.418165799036481</v>
       </c>
       <c r="E18" t="n">
-        <v>19.56699750884825</v>
+        <v>18.35012122943433</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.881804182023244</v>
+        <v>2.371342857268874</v>
       </c>
       <c r="C19" t="n">
-        <v>11.76013976467761</v>
+        <v>10.35144961880794</v>
       </c>
       <c r="D19" t="n">
-        <v>6.785751774460571</v>
+        <v>6.535376657446508</v>
       </c>
       <c r="E19" t="n">
-        <v>20.42769572116142</v>
+        <v>19.25816913352332</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.11707020186895</v>
+        <v>2.704420400888689</v>
       </c>
       <c r="C20" t="n">
-        <v>13.48439307512333</v>
+        <v>12.02392555533168</v>
       </c>
       <c r="D20" t="n">
-        <v>7.266680522339957</v>
+        <v>6.970605049693203</v>
       </c>
       <c r="E20" t="n">
-        <v>22.86814379933223</v>
+        <v>21.69895100591357</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.273336589885156</v>
+        <v>1.647735894376719</v>
       </c>
       <c r="C21" t="n">
-        <v>9.892629829228198</v>
+        <v>8.95986151794626</v>
       </c>
       <c r="D21" t="n">
-        <v>6.071824843932291</v>
+        <v>5.793921521291146</v>
       </c>
       <c r="E21" t="n">
-        <v>17.23779126304564</v>
+        <v>16.40151893361412</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_24_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_24_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.275060966125711</v>
+        <v>1.27091799081379</v>
       </c>
       <c r="C3" t="n">
-        <v>4.589912900096949</v>
+        <v>4.694203958719088</v>
       </c>
       <c r="D3" t="n">
-        <v>6.090532140371354</v>
+        <v>6.040629904564488</v>
       </c>
       <c r="E3" t="n">
-        <v>11.95550600659401</v>
+        <v>12.00575185409737</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.428978371471767</v>
+        <v>1.433014546688453</v>
       </c>
       <c r="C4" t="n">
-        <v>4.996005041195627</v>
+        <v>5.302795312568679</v>
       </c>
       <c r="D4" t="n">
-        <v>6.340917895328012</v>
+        <v>6.226180026388591</v>
       </c>
       <c r="E4" t="n">
-        <v>12.7659013079954</v>
+        <v>12.96198988564572</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.629077335286161</v>
+        <v>1.65319094089226</v>
       </c>
       <c r="C5" t="n">
-        <v>5.477881023959051</v>
+        <v>6.087449888989515</v>
       </c>
       <c r="D5" t="n">
-        <v>6.652358520160996</v>
+        <v>6.470528907356505</v>
       </c>
       <c r="E5" t="n">
-        <v>13.75931687940621</v>
+        <v>14.21116973723828</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.859792399268976</v>
+        <v>1.921306233149164</v>
       </c>
       <c r="C6" t="n">
-        <v>6.024707621575774</v>
+        <v>7.038676882104935</v>
       </c>
       <c r="D6" t="n">
-        <v>6.960599759071707</v>
+        <v>6.714581559887216</v>
       </c>
       <c r="E6" t="n">
-        <v>14.84509977991646</v>
+        <v>15.67456467514132</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.132440769056644</v>
+        <v>2.218692926431706</v>
       </c>
       <c r="C7" t="n">
-        <v>6.664251023173373</v>
+        <v>8.158465628102372</v>
       </c>
       <c r="D7" t="n">
-        <v>7.282582060514582</v>
+        <v>6.986588575550397</v>
       </c>
       <c r="E7" t="n">
-        <v>16.0792738527446</v>
+        <v>17.36374713008448</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.346305374554549</v>
+        <v>1.417192796589574</v>
       </c>
       <c r="C8" t="n">
-        <v>4.271084787716307</v>
+        <v>5.786933277659013</v>
       </c>
       <c r="D8" t="n">
-        <v>5.515830729315001</v>
+        <v>5.131001739987717</v>
       </c>
       <c r="E8" t="n">
-        <v>11.13322089158586</v>
+        <v>12.3351278142363</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.717807777775094</v>
+        <v>1.789158066758476</v>
       </c>
       <c r="C9" t="n">
-        <v>5.104862740965074</v>
+        <v>7.260815767470565</v>
       </c>
       <c r="D9" t="n">
-        <v>5.988413404084325</v>
+        <v>5.455290801723307</v>
       </c>
       <c r="E9" t="n">
-        <v>12.81108392282449</v>
+        <v>14.50526463595235</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.116087767268582</v>
+        <v>2.169110158906614</v>
       </c>
       <c r="C10" t="n">
-        <v>6.0796683860296</v>
+        <v>8.958675057055082</v>
       </c>
       <c r="D10" t="n">
-        <v>6.492002356976762</v>
+        <v>5.850777261913698</v>
       </c>
       <c r="E10" t="n">
-        <v>14.68775851027494</v>
+        <v>16.97856247787539</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.532340399485766</v>
+        <v>2.543458388022851</v>
       </c>
       <c r="C11" t="n">
-        <v>7.155222090467995</v>
+        <v>10.79560181316077</v>
       </c>
       <c r="D11" t="n">
-        <v>6.953260850350564</v>
+        <v>6.183356723857197</v>
       </c>
       <c r="E11" t="n">
-        <v>16.64082334030432</v>
+        <v>19.52241692504082</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.960599990926244</v>
+        <v>2.922891455782144</v>
       </c>
       <c r="C12" t="n">
-        <v>8.328122269085624</v>
+        <v>12.69073194444866</v>
       </c>
       <c r="D12" t="n">
-        <v>7.410924279531399</v>
+        <v>6.490045083384489</v>
       </c>
       <c r="E12" t="n">
-        <v>18.69964653954327</v>
+        <v>22.10366848361529</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.397490829692132</v>
+        <v>3.273539086811851</v>
       </c>
       <c r="C13" t="n">
-        <v>9.609075176853016</v>
+        <v>14.64641292421334</v>
       </c>
       <c r="D13" t="n">
-        <v>7.870372299650911</v>
+        <v>6.870377853780753</v>
       </c>
       <c r="E13" t="n">
-        <v>20.87693830619606</v>
+        <v>24.79032986480594</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.97621885874066</v>
+        <v>1.887920470220702</v>
       </c>
       <c r="C14" t="n">
-        <v>6.860924196174749</v>
+        <v>10.18588768596376</v>
       </c>
       <c r="D14" t="n">
-        <v>5.990447776727273</v>
+        <v>5.249208625066846</v>
       </c>
       <c r="E14" t="n">
-        <v>14.82759083164268</v>
+        <v>17.32301678125131</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.06214141781634</v>
+        <v>1.928456832929052</v>
       </c>
       <c r="C15" t="n">
-        <v>7.40197517346221</v>
+        <v>11.16024282999759</v>
       </c>
       <c r="D15" t="n">
-        <v>6.001443351014837</v>
+        <v>5.161823261911837</v>
       </c>
       <c r="E15" t="n">
-        <v>15.46555994229339</v>
+        <v>18.25052292483849</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.44237230367113</v>
+        <v>2.219849369026548</v>
       </c>
       <c r="C16" t="n">
-        <v>8.778189105275388</v>
+        <v>13.28148545960959</v>
       </c>
       <c r="D16" t="n">
-        <v>6.465957277279215</v>
+        <v>5.458163806438737</v>
       </c>
       <c r="E16" t="n">
-        <v>17.68651868622573</v>
+        <v>20.95949863507488</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.988107823439088</v>
+        <v>1.766704081177348</v>
       </c>
       <c r="C17" t="n">
-        <v>8.202030830084063</v>
+        <v>12.27128670689371</v>
       </c>
       <c r="D17" t="n">
-        <v>6.002199296747107</v>
+        <v>4.974564704803801</v>
       </c>
       <c r="E17" t="n">
-        <v>16.19233795027026</v>
+        <v>19.01255549287486</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.314951269136937</v>
+        <v>1.998887413231718</v>
       </c>
       <c r="C18" t="n">
-        <v>9.617004161260907</v>
+        <v>14.36445135216425</v>
       </c>
       <c r="D18" t="n">
-        <v>6.418165799036481</v>
+        <v>5.266399027368208</v>
       </c>
       <c r="E18" t="n">
-        <v>18.35012122943433</v>
+        <v>21.62973779276417</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.371342857268874</v>
+        <v>1.989217198344888</v>
       </c>
       <c r="C19" t="n">
-        <v>10.35144961880794</v>
+        <v>15.38787424645634</v>
       </c>
       <c r="D19" t="n">
-        <v>6.535376657446508</v>
+        <v>5.2748813275329</v>
       </c>
       <c r="E19" t="n">
-        <v>19.25816913352332</v>
+        <v>22.65197277233413</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.704420400888689</v>
+        <v>2.195943812428138</v>
       </c>
       <c r="C20" t="n">
-        <v>12.02392555533168</v>
+        <v>17.6123967345551</v>
       </c>
       <c r="D20" t="n">
-        <v>6.970605049693203</v>
+        <v>5.538215514243022</v>
       </c>
       <c r="E20" t="n">
-        <v>21.69895100591357</v>
+        <v>25.34655606122626</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.647735894376719</v>
+        <v>1.296790542539612</v>
       </c>
       <c r="C21" t="n">
-        <v>8.95986151794626</v>
+        <v>12.82307800406563</v>
       </c>
       <c r="D21" t="n">
-        <v>5.793921521291146</v>
+        <v>4.567875718319559</v>
       </c>
       <c r="E21" t="n">
-        <v>16.40151893361412</v>
+        <v>18.6877442649248</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_24_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_24_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.27091799081379</v>
+        <v>2.581387300476008</v>
       </c>
       <c r="C3" t="n">
-        <v>4.694203958719088</v>
+        <v>7.731898476307899</v>
       </c>
       <c r="D3" t="n">
-        <v>6.040629904564488</v>
+        <v>8.198504160883237</v>
       </c>
       <c r="E3" t="n">
-        <v>12.00575185409737</v>
+        <v>18.51178993766715</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.433014546688453</v>
+        <v>1.050615924911531</v>
       </c>
       <c r="C4" t="n">
-        <v>5.302795312568679</v>
+        <v>4.536658870755498</v>
       </c>
       <c r="D4" t="n">
-        <v>6.226180026388591</v>
+        <v>5.854593437361053</v>
       </c>
       <c r="E4" t="n">
-        <v>12.96198988564572</v>
+        <v>11.44186823302808</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.65319094089226</v>
+        <v>1.123293217417741</v>
       </c>
       <c r="C5" t="n">
-        <v>6.087449888989515</v>
+        <v>5.194261417278726</v>
       </c>
       <c r="D5" t="n">
-        <v>6.470528907356505</v>
+        <v>6.173239621535239</v>
       </c>
       <c r="E5" t="n">
-        <v>14.21116973723828</v>
+        <v>12.49079425623171</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.921306233149164</v>
+        <v>1.19850197631794</v>
       </c>
       <c r="C6" t="n">
-        <v>7.038676882104935</v>
+        <v>6.041894268218105</v>
       </c>
       <c r="D6" t="n">
-        <v>6.714581559887216</v>
+        <v>6.527588794647402</v>
       </c>
       <c r="E6" t="n">
-        <v>15.67456467514132</v>
+        <v>13.76798503918345</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.218692926431706</v>
+        <v>1.27220685061354</v>
       </c>
       <c r="C7" t="n">
-        <v>8.158465628102372</v>
+        <v>7.08953607699586</v>
       </c>
       <c r="D7" t="n">
-        <v>6.986588575550397</v>
+        <v>6.903735993159317</v>
       </c>
       <c r="E7" t="n">
-        <v>17.36374713008448</v>
+        <v>15.26547892076872</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.417192796589574</v>
+        <v>1.357979493557441</v>
       </c>
       <c r="C8" t="n">
-        <v>5.786933277659013</v>
+        <v>8.396592689031827</v>
       </c>
       <c r="D8" t="n">
-        <v>5.131001739987717</v>
+        <v>7.334803149690674</v>
       </c>
       <c r="E8" t="n">
-        <v>12.3351278142363</v>
+        <v>17.08937533227994</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.789158066758476</v>
+        <v>1.429089781268273</v>
       </c>
       <c r="C9" t="n">
-        <v>7.260815767470565</v>
+        <v>9.901683516795012</v>
       </c>
       <c r="D9" t="n">
-        <v>5.455290801723307</v>
+        <v>7.700589121103453</v>
       </c>
       <c r="E9" t="n">
-        <v>14.50526463595235</v>
+        <v>19.03136241916674</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.169110158906614</v>
+        <v>0.9204081076854697</v>
       </c>
       <c r="C10" t="n">
-        <v>8.958675057055082</v>
+        <v>7.385894146066646</v>
       </c>
       <c r="D10" t="n">
-        <v>5.850777261913698</v>
+        <v>6.057324430340564</v>
       </c>
       <c r="E10" t="n">
-        <v>16.97856247787539</v>
+        <v>14.36362668409268</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.543458388022851</v>
+        <v>0.8311181539842222</v>
       </c>
       <c r="C11" t="n">
-        <v>10.79560181316077</v>
+        <v>8.131482440056885</v>
       </c>
       <c r="D11" t="n">
-        <v>6.183356723857197</v>
+        <v>5.902512634857885</v>
       </c>
       <c r="E11" t="n">
-        <v>19.52241692504082</v>
+        <v>14.86511322889899</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.922891455782144</v>
+        <v>0.8679533278475625</v>
       </c>
       <c r="C12" t="n">
-        <v>12.69073194444866</v>
+        <v>9.898206156188319</v>
       </c>
       <c r="D12" t="n">
-        <v>6.490045083384489</v>
+        <v>6.272091558121598</v>
       </c>
       <c r="E12" t="n">
-        <v>22.10366848361529</v>
+        <v>17.03825104215748</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.273539086811851</v>
+        <v>0.6713190801639689</v>
       </c>
       <c r="C13" t="n">
-        <v>14.64641292421334</v>
+        <v>9.685500698586205</v>
       </c>
       <c r="D13" t="n">
-        <v>6.870377853780753</v>
+        <v>5.698161850218912</v>
       </c>
       <c r="E13" t="n">
-        <v>24.79032986480594</v>
+        <v>16.05498162896908</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.887920470220702</v>
+        <v>0.7038836515138357</v>
       </c>
       <c r="C14" t="n">
-        <v>10.18588768596376</v>
+        <v>11.59238853445295</v>
       </c>
       <c r="D14" t="n">
-        <v>5.249208625066846</v>
+        <v>6.03924063762834</v>
       </c>
       <c r="E14" t="n">
-        <v>17.32301678125131</v>
+        <v>18.33551282359513</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.928456832929052</v>
+        <v>0.6622771838078559</v>
       </c>
       <c r="C15" t="n">
-        <v>11.16024282999759</v>
+        <v>12.74078791149566</v>
       </c>
       <c r="D15" t="n">
-        <v>5.161823261911837</v>
+        <v>6.052317517048907</v>
       </c>
       <c r="E15" t="n">
-        <v>18.25052292483849</v>
+        <v>19.45538261235243</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.219849369026548</v>
+        <v>0.7056017099962676</v>
       </c>
       <c r="C16" t="n">
-        <v>13.28148545960959</v>
+        <v>14.947874560367</v>
       </c>
       <c r="D16" t="n">
-        <v>5.458163806438737</v>
+        <v>6.401211016184138</v>
       </c>
       <c r="E16" t="n">
-        <v>20.95949863507488</v>
+        <v>22.05468728654741</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.766704081177348</v>
+        <v>0.4204040019125691</v>
       </c>
       <c r="C17" t="n">
-        <v>12.27128670689371</v>
+        <v>11.20104426458609</v>
       </c>
       <c r="D17" t="n">
-        <v>4.974564704803801</v>
+        <v>5.290226044150278</v>
       </c>
       <c r="E17" t="n">
-        <v>19.01255549287486</v>
+        <v>16.91167431064894</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.998887413231718</v>
+        <v>0.3139530983410875</v>
       </c>
       <c r="C18" t="n">
-        <v>14.36445135216425</v>
+        <v>10.23330610007888</v>
       </c>
       <c r="D18" t="n">
-        <v>5.266399027368208</v>
+        <v>4.763351503712141</v>
       </c>
       <c r="E18" t="n">
-        <v>21.62973779276417</v>
+        <v>15.31061070213211</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.989217198344888</v>
+        <v>0.3554123038914303</v>
       </c>
       <c r="C19" t="n">
-        <v>15.38787424645634</v>
+        <v>12.68396435437386</v>
       </c>
       <c r="D19" t="n">
-        <v>5.2748813275329</v>
+        <v>5.194790349820446</v>
       </c>
       <c r="E19" t="n">
-        <v>22.65197277233413</v>
+        <v>18.23416700808573</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.195943812428138</v>
+        <v>0.3918842311041993</v>
       </c>
       <c r="C20" t="n">
-        <v>17.6123967345551</v>
+        <v>15.2172366779812</v>
       </c>
       <c r="D20" t="n">
-        <v>5.538215514243022</v>
+        <v>5.690062431658877</v>
       </c>
       <c r="E20" t="n">
-        <v>25.34655606122626</v>
+        <v>21.29918334074427</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.296790542539612</v>
+        <v>0.4214446544790708</v>
       </c>
       <c r="C21" t="n">
-        <v>12.82307800406563</v>
+        <v>17.75096060553249</v>
       </c>
       <c r="D21" t="n">
-        <v>4.567875718319559</v>
+        <v>6.073974871404591</v>
       </c>
       <c r="E21" t="n">
-        <v>18.6877442649248</v>
+        <v>24.24638013141615</v>
       </c>
     </row>
   </sheetData>
